--- a/app/reports/NTIP_research.xlsx
+++ b/app/reports/NTIP_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-20 17:39 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-21 17:38 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.044509997</v>
+        <v>0.04450999999999999</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NTIP_research.xlsx
+++ b/app/reports/NTIP_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-21 17:38 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-22 17:39 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04450999999999999</v>
+        <v>0.04508999824523926</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>22864593.19727891</v>
+        <v>22864591.89189189</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="38">
@@ -1508,7 +1508,7 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>33610952</v>
+        <v>33839596</v>
       </c>
       <c r="D5" s="31" t="n"/>
       <c r="E5" s="31" t="n">
@@ -1528,10 +1528,10 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>41438100</v>
+        <v>41954640</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>18.05</v>
+        <v>18.275</v>
       </c>
       <c r="E6" s="33" t="n">
         <v>9.596</v>
@@ -1552,10 +1552,10 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>65652052</v>
+        <v>66510680</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>41.416664</v>
+        <v>41.958332</v>
       </c>
       <c r="E7" s="33" t="n">
         <v>29.101</v>
@@ -1576,7 +1576,7 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>66771636</v>
+        <v>64921684</v>
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n">
@@ -1598,7 +1598,7 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>24411044</v>
+        <v>24341332</v>
       </c>
       <c r="D9" s="33" t="n"/>
       <c r="E9" s="33" t="n">
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>33506218</v>
+        <v>43529448</v>
       </c>
       <c r="D10" s="33" t="n"/>
       <c r="E10" s="33" t="n">
@@ -1642,7 +1642,7 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>15041165</v>
+        <v>13874378</v>
       </c>
       <c r="D11" s="33" t="n"/>
       <c r="E11" s="33" t="n">
@@ -1664,7 +1664,7 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>28238506</v>
+        <v>30794724</v>
       </c>
       <c r="D12" s="33" t="n"/>
       <c r="E12" s="33" t="n">
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>23152058</v>
+        <v>23200202</v>
       </c>
       <c r="D13" s="33" t="n"/>
       <c r="E13" s="33" t="n">

--- a/app/reports/NTIP_research.xlsx
+++ b/app/reports/NTIP_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-22 17:39 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-23 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>1.48</v>
+        <v>1.485</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04508999824523926</v>
+        <v>0.04484999656677246</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>22864591.89189189</v>
+        <v>22864592.59259259</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>1.48</v>
+        <v>1.485</v>
       </c>
     </row>
     <row r="38">
@@ -1508,11 +1508,11 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>33839596</v>
+        <v>33953920</v>
       </c>
       <c r="D5" s="31" t="n"/>
       <c r="E5" s="31" t="n">
-        <v>0.25</v>
+        <v>0.19</v>
       </c>
       <c r="F5" s="31" t="n"/>
     </row>
@@ -1528,10 +1528,10 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>41954640</v>
+        <v>41552884</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>18.275</v>
+        <v>18.099998</v>
       </c>
       <c r="E6" s="33" t="n">
         <v>9.596</v>
@@ -1552,16 +1552,16 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>66510680</v>
+        <v>66774876</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>41.958332</v>
+        <v>42.125</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>29.101</v>
+        <v>29.555</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>1.308</v>
+        <v>1.328</v>
       </c>
     </row>
     <row r="8">
@@ -1576,14 +1576,14 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>64921684</v>
+        <v>64603728</v>
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n">
-        <v>8.467000000000001</v>
+        <v>8.01</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>2.816</v>
+        <v>2.664</v>
       </c>
     </row>
     <row r="9">
@@ -1598,14 +1598,14 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>24341332</v>
+        <v>24980364</v>
       </c>
       <c r="D9" s="33" t="n"/>
       <c r="E9" s="33" t="n">
-        <v>-11.303</v>
+        <v>-11.117</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>2.457</v>
+        <v>2.416</v>
       </c>
     </row>
     <row r="10">
@@ -1620,14 +1620,14 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>43529448</v>
+        <v>45534092</v>
       </c>
       <c r="D10" s="33" t="n"/>
       <c r="E10" s="33" t="n">
-        <v>-5.98</v>
+        <v>-7.349</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>0.234</v>
+        <v>0.287</v>
       </c>
     </row>
     <row r="11">
@@ -1642,14 +1642,14 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>13874378</v>
+        <v>14112922</v>
       </c>
       <c r="D11" s="33" t="n"/>
       <c r="E11" s="33" t="n">
-        <v>-1.395</v>
+        <v>-1.313</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>10.02</v>
+        <v>9.43</v>
       </c>
     </row>
     <row r="12">
@@ -1664,14 +1664,14 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>30794724</v>
+        <v>29292182</v>
       </c>
       <c r="D12" s="33" t="n"/>
       <c r="E12" s="33" t="n">
-        <v>12.564</v>
+        <v>12.819</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>0.382</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="13">
@@ -1686,14 +1686,14 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>23200202</v>
+        <v>21837984</v>
       </c>
       <c r="D13" s="33" t="n"/>
       <c r="E13" s="33" t="n">
-        <v>-4.264</v>
+        <v>-4.224</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>0.351</v>
+        <v>0.348</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/NTIP_research.xlsx
+++ b/app/reports/NTIP_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-23 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-25 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>1.485</v>
+        <v>1.4682</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04484999656677246</v>
+        <v>0.04383999824523926</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>22864592.59259259</v>
+        <v>22864590.65522408</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>1.485</v>
+        <v>1.4682</v>
       </c>
     </row>
     <row r="38">
@@ -1508,11 +1508,11 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>33953920</v>
+        <v>33569792</v>
       </c>
       <c r="D5" s="31" t="n"/>
       <c r="E5" s="31" t="n">
-        <v>0.19</v>
+        <v>0.25</v>
       </c>
       <c r="F5" s="31" t="n"/>
     </row>
@@ -1528,16 +1528,16 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>41552884</v>
+        <v>41839852</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>18.099998</v>
+        <v>18.225</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>9.596</v>
+        <v>9.724</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>0.734</v>
+        <v>0.744</v>
       </c>
     </row>
     <row r="7">
@@ -1552,16 +1552,16 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>66774876</v>
+        <v>64235980</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>42.125</v>
+        <v>40.523335</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>29.555</v>
+        <v>28.234</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>1.328</v>
+        <v>1.269</v>
       </c>
     </row>
     <row r="8">
@@ -1576,14 +1576,14 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>64603728</v>
+        <v>66771636</v>
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n">
-        <v>8.01</v>
+        <v>8.608000000000001</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>2.664</v>
+        <v>2.863</v>
       </c>
     </row>
     <row r="9">
@@ -1598,14 +1598,14 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>24980364</v>
+        <v>24012134</v>
       </c>
       <c r="D9" s="33" t="n"/>
       <c r="E9" s="33" t="n">
-        <v>-11.117</v>
+        <v>-11.226</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>2.416</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="10">
@@ -1620,14 +1620,14 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>45534092</v>
+        <v>41095232</v>
       </c>
       <c r="D10" s="33" t="n"/>
       <c r="E10" s="33" t="n">
-        <v>-7.349</v>
+        <v>-7.622</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>0.287</v>
+        <v>0.298</v>
       </c>
     </row>
     <row r="11">
@@ -1642,14 +1642,14 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>14112922</v>
+        <v>13031701</v>
       </c>
       <c r="D11" s="33" t="n"/>
       <c r="E11" s="33" t="n">
-        <v>-1.313</v>
+        <v>-1.171</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>9.43</v>
+        <v>8.412000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -1664,14 +1664,14 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>29292182</v>
+        <v>28870712</v>
       </c>
       <c r="D12" s="33" t="n"/>
       <c r="E12" s="33" t="n">
-        <v>12.819</v>
+        <v>12.706</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>0.39</v>
+        <v>0.386</v>
       </c>
     </row>
     <row r="13">
@@ -1686,14 +1686,14 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>21837984</v>
+        <v>23732630</v>
       </c>
       <c r="D13" s="33" t="n"/>
       <c r="E13" s="33" t="n">
-        <v>-4.224</v>
+        <v>-4.277</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>0.348</v>
+        <v>0.352</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/NTIP_research.xlsx
+++ b/app/reports/NTIP_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-25 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-06 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>1.4682</v>
+        <v>1.47</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04383999824523926</v>
+        <v>0.04480999946594239</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>22864590.65522408</v>
+        <v>22864593.19727891</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>1.4682</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="38">
@@ -1508,11 +1508,11 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>33569792</v>
+        <v>33610952</v>
       </c>
       <c r="D5" s="31" t="n"/>
       <c r="E5" s="31" t="n">
-        <v>0.25</v>
+        <v>0.13</v>
       </c>
       <c r="F5" s="31" t="n"/>
     </row>
@@ -1552,16 +1552,16 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>64235980</v>
+        <v>69217344</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>40.523335</v>
+        <v>43.665836</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>28.234</v>
+        <v>31.164</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>1.269</v>
+        <v>1.401</v>
       </c>
     </row>
     <row r="8">
@@ -1576,14 +1576,14 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>66771636</v>
+        <v>65586512</v>
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n">
-        <v>8.608000000000001</v>
+        <v>8.31</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>2.863</v>
+        <v>2.764</v>
       </c>
     </row>
     <row r="9">
@@ -1598,14 +1598,14 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>24012134</v>
+        <v>23624842</v>
       </c>
       <c r="D9" s="33" t="n"/>
       <c r="E9" s="33" t="n">
-        <v>-11.226</v>
+        <v>-11.443</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>2.44</v>
+        <v>2.487</v>
       </c>
     </row>
     <row r="10">
@@ -1620,14 +1620,14 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>41095232</v>
+        <v>44818148</v>
       </c>
       <c r="D10" s="33" t="n"/>
       <c r="E10" s="33" t="n">
-        <v>-7.622</v>
+        <v>-7.896</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>0.298</v>
+        <v>0.309</v>
       </c>
     </row>
     <row r="11">
@@ -1642,14 +1642,14 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>13031701</v>
+        <v>13840672</v>
       </c>
       <c r="D11" s="33" t="n"/>
       <c r="E11" s="33" t="n">
-        <v>-1.171</v>
+        <v>-1.033</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>8.412000000000001</v>
+        <v>7.42</v>
       </c>
     </row>
     <row r="12">
@@ -1664,14 +1664,14 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>28870712</v>
+        <v>26868728</v>
       </c>
       <c r="D12" s="33" t="n"/>
       <c r="E12" s="33" t="n">
-        <v>12.706</v>
+        <v>12.422</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>0.386</v>
+        <v>0.378</v>
       </c>
     </row>
     <row r="13">
@@ -1686,14 +1686,14 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>23732630</v>
+        <v>23795152</v>
       </c>
       <c r="D13" s="33" t="n"/>
       <c r="E13" s="33" t="n">
-        <v>-4.277</v>
+        <v>-4.312</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>0.352</v>
+        <v>0.355</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/NTIP_research.xlsx
+++ b/app/reports/NTIP_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-06 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-07 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04480999946594239</v>
+        <v>0.04525000095367432</v>
       </c>
     </row>
     <row r="6">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="D5" s="31" t="n"/>
       <c r="E5" s="31" t="n">
-        <v>0.13</v>
+        <v>0.25</v>
       </c>
       <c r="F5" s="31" t="n"/>
     </row>
@@ -1528,16 +1528,16 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>41839852</v>
+        <v>41237224</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>18.225</v>
+        <v>17.9625</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>9.724</v>
+        <v>9.574</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>0.744</v>
+        <v>0.732</v>
       </c>
     </row>
     <row r="7">
@@ -1552,16 +1552,16 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>69217344</v>
+        <v>68238512</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>43.665836</v>
+        <v>43.048336</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>31.164</v>
+        <v>30.38</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>1.401</v>
+        <v>1.365</v>
       </c>
     </row>
     <row r="8">
@@ -1576,14 +1576,14 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>65586512</v>
+        <v>61886612</v>
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n">
-        <v>8.31</v>
+        <v>8.423999999999999</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>2.764</v>
+        <v>2.802</v>
       </c>
     </row>
     <row r="9">
@@ -1598,14 +1598,14 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>23624842</v>
+        <v>23431196</v>
       </c>
       <c r="D9" s="33" t="n"/>
       <c r="E9" s="33" t="n">
-        <v>-11.443</v>
+        <v>-11.225</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>2.487</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="10">
@@ -1620,14 +1620,14 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>44818148</v>
+        <v>42383936</v>
       </c>
       <c r="D10" s="33" t="n"/>
       <c r="E10" s="33" t="n">
-        <v>-7.896</v>
+        <v>-7.841</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>0.309</v>
+        <v>0.306</v>
       </c>
     </row>
     <row r="11">
@@ -1642,14 +1642,14 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>13840672</v>
+        <v>13298764</v>
       </c>
       <c r="D11" s="33" t="n"/>
       <c r="E11" s="33" t="n">
-        <v>-1.033</v>
+        <v>-1.241</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>7.42</v>
+        <v>8.914999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1668,10 +1668,10 @@
       </c>
       <c r="D12" s="33" t="n"/>
       <c r="E12" s="33" t="n">
-        <v>12.422</v>
+        <v>12.309</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>0.378</v>
+        <v>0.374</v>
       </c>
     </row>
     <row r="13">
@@ -1686,14 +1686,14 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>23795152</v>
+        <v>23599202</v>
       </c>
       <c r="D13" s="33" t="n"/>
       <c r="E13" s="33" t="n">
-        <v>-4.312</v>
+        <v>-4.292</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>0.355</v>
+        <v>0.353</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/NTIP_research.xlsx
+++ b/app/reports/NTIP_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-07 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-08 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>1.47</v>
+        <v>1.445</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04525000095367432</v>
+        <v>0.04577000141143799</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>22864593.19727891</v>
+        <v>22864592.38754325</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>1.47</v>
+        <v>1.445</v>
       </c>
     </row>
     <row r="38">
@@ -1508,11 +1508,11 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>33610952</v>
+        <v>33039336</v>
       </c>
       <c r="D5" s="31" t="n"/>
       <c r="E5" s="31" t="n">
-        <v>0.25</v>
+        <v>0.54</v>
       </c>
       <c r="F5" s="31" t="n"/>
     </row>
@@ -1528,16 +1528,16 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>41237224</v>
+        <v>41581584</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>17.9625</v>
+        <v>18.1125</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>9.574</v>
+        <v>9.734999999999999</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>0.732</v>
+        <v>0.745</v>
       </c>
     </row>
     <row r="7">
@@ -1552,16 +1552,16 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>68238512</v>
+        <v>68939944</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>43.048336</v>
+        <v>43.490837</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>30.38</v>
+        <v>30.793</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>1.365</v>
+        <v>1.384</v>
       </c>
     </row>
     <row r="8">
@@ -1576,14 +1576,14 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>61886612</v>
+        <v>63592032</v>
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n">
-        <v>8.423999999999999</v>
+        <v>8.236000000000001</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>2.802</v>
+        <v>2.739</v>
       </c>
     </row>
     <row r="9">
@@ -1598,14 +1598,14 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>23431196</v>
+        <v>23129106</v>
       </c>
       <c r="D9" s="33" t="n"/>
       <c r="E9" s="33" t="n">
-        <v>-11.225</v>
+        <v>-11.298</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>2.44</v>
+        <v>2.456</v>
       </c>
     </row>
     <row r="10">
@@ -1620,14 +1620,14 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>42383936</v>
+        <v>40952044</v>
       </c>
       <c r="D10" s="33" t="n"/>
       <c r="E10" s="33" t="n">
-        <v>-7.841</v>
+        <v>-7.622</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>0.306</v>
+        <v>0.298</v>
       </c>
     </row>
     <row r="11">
@@ -1642,14 +1642,14 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>13298764</v>
+        <v>12961693</v>
       </c>
       <c r="D11" s="33" t="n"/>
       <c r="E11" s="33" t="n">
-        <v>-1.241</v>
+        <v>-1.18</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>8.914999999999999</v>
+        <v>8.473000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -1664,14 +1664,14 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>26868728</v>
+        <v>26025788</v>
       </c>
       <c r="D12" s="33" t="n"/>
       <c r="E12" s="33" t="n">
-        <v>12.309</v>
+        <v>12.365</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>0.374</v>
+        <v>0.376</v>
       </c>
     </row>
     <row r="13">
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>23599202</v>
+        <v>23286818</v>
       </c>
       <c r="D13" s="33" t="n"/>
       <c r="E13" s="33" t="n">

--- a/app/reports/NTIP_research.xlsx
+++ b/app/reports/NTIP_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-08 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-09 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>1.445</v>
+        <v>1.4499</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04577000141143799</v>
+        <v>0.04532999992370605</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>22864592.38754325</v>
+        <v>22864592.0408304</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>1.445</v>
+        <v>1.4499</v>
       </c>
     </row>
     <row r="38">
@@ -1508,11 +1508,11 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>33039336</v>
+        <v>33151372</v>
       </c>
       <c r="D5" s="31" t="n"/>
       <c r="E5" s="31" t="n">
-        <v>0.54</v>
+        <v>0.31</v>
       </c>
       <c r="F5" s="31" t="n"/>
     </row>
@@ -1528,16 +1528,16 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>41581584</v>
+        <v>41897248</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>18.1125</v>
+        <v>18.25</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>9.734999999999999</v>
+        <v>9.574</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>0.745</v>
+        <v>0.732</v>
       </c>
     </row>
     <row r="7">
@@ -1552,16 +1552,16 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>68939944</v>
+        <v>68161888</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>43.490837</v>
+        <v>43</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>30.793</v>
+        <v>30.463</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>1.384</v>
+        <v>1.369</v>
       </c>
     </row>
     <row r="8">
@@ -1576,14 +1576,14 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>63592032</v>
+        <v>63563128</v>
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n">
-        <v>8.236000000000001</v>
+        <v>8.308999999999999</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>2.739</v>
+        <v>2.763</v>
       </c>
     </row>
     <row r="9">
@@ -1598,14 +1598,14 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>23129106</v>
+        <v>22273190</v>
       </c>
       <c r="D9" s="33" t="n"/>
       <c r="E9" s="33" t="n">
-        <v>-11.298</v>
+        <v>-11.129</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>2.456</v>
+        <v>2.419</v>
       </c>
     </row>
     <row r="10">
@@ -1620,14 +1620,14 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>40952044</v>
+        <v>41238424</v>
       </c>
       <c r="D10" s="33" t="n"/>
       <c r="E10" s="33" t="n">
-        <v>-7.622</v>
+        <v>-7.403</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>0.298</v>
+        <v>0.289</v>
       </c>
     </row>
     <row r="11">
@@ -1642,14 +1642,14 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>12961693</v>
+        <v>13446557</v>
       </c>
       <c r="D11" s="33" t="n"/>
       <c r="E11" s="33" t="n">
-        <v>-1.18</v>
+        <v>-1.151</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>8.473000000000001</v>
+        <v>8.268000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -1664,14 +1664,14 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>26025788</v>
+        <v>26974094</v>
       </c>
       <c r="D12" s="33" t="n"/>
       <c r="E12" s="33" t="n">
-        <v>12.365</v>
+        <v>12.309</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>0.376</v>
+        <v>0.374</v>
       </c>
     </row>
     <row r="13">
@@ -1686,14 +1686,14 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>23286818</v>
+        <v>24309168</v>
       </c>
       <c r="D13" s="33" t="n"/>
       <c r="E13" s="33" t="n">
-        <v>-4.292</v>
+        <v>-4.269</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>0.353</v>
+        <v>0.351</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/NTIP_research.xlsx
+++ b/app/reports/NTIP_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-09 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-10 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>1.4499</v>
+        <v>1.44</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04532999992370605</v>
+        <v>0.04565000057220459</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>22864592.0408304</v>
+        <v>22864593.05555556</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>1.4499</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="38">
@@ -1508,11 +1508,11 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>33151372</v>
+        <v>32925014</v>
       </c>
       <c r="D5" s="31" t="n"/>
       <c r="E5" s="31" t="n">
-        <v>0.31</v>
+        <v>0.25</v>
       </c>
       <c r="F5" s="31" t="n"/>
     </row>
@@ -1528,10 +1528,10 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>41897248</v>
+        <v>41151132</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>18.25</v>
+        <v>17.925</v>
       </c>
       <c r="E6" s="33" t="n">
         <v>9.574</v>
@@ -1552,16 +1552,16 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>68161888</v>
+        <v>67369312</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>43</v>
+        <v>42.5</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>30.463</v>
+        <v>30.133</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>1.369</v>
+        <v>1.354</v>
       </c>
     </row>
     <row r="8">
@@ -1576,14 +1576,14 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>63563128</v>
+        <v>63736560</v>
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n">
-        <v>8.308999999999999</v>
+        <v>8.257</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>2.763</v>
+        <v>2.746</v>
       </c>
     </row>
     <row r="9">
@@ -1598,14 +1598,14 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>22273190</v>
+        <v>22036942</v>
       </c>
       <c r="D9" s="33" t="n"/>
       <c r="E9" s="33" t="n">
-        <v>-11.129</v>
+        <v>-11.07</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>2.419</v>
+        <v>2.406</v>
       </c>
     </row>
     <row r="10">
@@ -1620,14 +1620,14 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>41238424</v>
+        <v>38231456</v>
       </c>
       <c r="D10" s="33" t="n"/>
       <c r="E10" s="33" t="n">
-        <v>-7.403</v>
+        <v>-7.568</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>0.289</v>
+        <v>0.296</v>
       </c>
     </row>
     <row r="11">
@@ -1642,14 +1642,14 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>13446557</v>
+        <v>13643614</v>
       </c>
       <c r="D11" s="33" t="n"/>
       <c r="E11" s="33" t="n">
-        <v>-1.151</v>
+        <v>-1.181</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>8.268000000000001</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="12">
@@ -1664,14 +1664,14 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>26974094</v>
+        <v>26763360</v>
       </c>
       <c r="D12" s="33" t="n"/>
       <c r="E12" s="33" t="n">
-        <v>12.309</v>
+        <v>12.408</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>0.374</v>
+        <v>0.377</v>
       </c>
     </row>
     <row r="13">
@@ -1686,14 +1686,14 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>24309168</v>
+        <v>24985054</v>
       </c>
       <c r="D13" s="33" t="n"/>
       <c r="E13" s="33" t="n">
-        <v>-4.269</v>
+        <v>-4.357</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>0.351</v>
+        <v>0.358</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/NTIP_research.xlsx
+++ b/app/reports/NTIP_research.xlsx
@@ -595,7 +595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-10 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-28 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -656,7 +656,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>1.44</v>
+        <v>1.6243</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -734,67 +734,52 @@
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>comps_percentile</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Peer-relative ranking of P/E, EV/EBITDA, EV/Rev</t>
-        </is>
-      </c>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Honest caveats (read before acting)</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="3" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Honest caveats (read before acting)</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="n"/>
-      <c r="C16" s="3" t="n"/>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Lite DCF: 5y horizon, 70/30 equity/debt cap structure assumed, FCF growth from 3y trailing trend.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Lite DCF: 5y horizon, 70/30 equity/debt cap structure assumed, FCF growth from 3y trailing trend.</t>
+          <t>Peer set is FMP's algorithmic /stock-peers — may include weak comps for unusual business models.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Peer set is FMP's algorithmic /stock-peers — may include weak comps for unusual business models.</t>
+          <t>Net cash treatment uses cashAndShortTermInvestments (operating cash); excludes LT marketable</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Net cash treatment uses cashAndShortTermInvestments (operating cash); excludes LT marketable</t>
+          <t xml:space="preserve">  securities, which understates intrinsic for cash-rich companies like AAPL (~$80B in LT inv).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  securities, which understates intrinsic for cash-rich companies like AAPL (~$80B in LT inv).</t>
+          <t>Margin of safety is normalized to 0..1; flip to the DCF tab for the raw % gap.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Margin of safety is normalized to 0..1; flip to the DCF tab for the raw % gap.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>This is a SIGNAL screen, not an investment thesis. Verify with primary filings before acting.</t>
         </is>
@@ -805,7 +790,6 @@
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A1:C2"/>
-    <mergeCell ref="A22:C22"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="A3:C3"/>
@@ -813,6 +797,7 @@
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A15:C15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -879,7 +864,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04565000057220459</v>
+        <v>0.04595999717712403</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1193,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>22864593.05555556</v>
+        <v>22944827.92587576</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1214,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>1.44</v>
+        <v>1.6243</v>
       </c>
     </row>
     <row r="38">
@@ -1508,11 +1493,11 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>32925014</v>
+        <v>37269284</v>
       </c>
       <c r="D5" s="31" t="n"/>
       <c r="E5" s="31" t="n">
-        <v>0.25</v>
+        <v>-0.51</v>
       </c>
       <c r="F5" s="31" t="n"/>
     </row>
@@ -1528,16 +1513,16 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>41151132</v>
+        <v>36502260</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>17.925</v>
+        <v>15.900001</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>9.574</v>
+        <v>8.781000000000001</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>0.732</v>
+        <v>0.672</v>
       </c>
     </row>
     <row r="7">
@@ -1552,16 +1537,16 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>67369312</v>
+        <v>66378588</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>42.5</v>
+        <v>41.875</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>30.133</v>
+        <v>28.317</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>1.354</v>
+        <v>1.273</v>
       </c>
     </row>
     <row r="8">
@@ -1576,14 +1561,14 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>63736560</v>
+        <v>70240288</v>
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n">
-        <v>8.257</v>
+        <v>8.731999999999999</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>2.746</v>
+        <v>2.904</v>
       </c>
     </row>
     <row r="9">
@@ -1598,14 +1583,14 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>22036942</v>
+        <v>18009100</v>
       </c>
       <c r="D9" s="33" t="n"/>
       <c r="E9" s="33" t="n">
-        <v>-11.07</v>
+        <v>-10.767</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>2.406</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="10">
@@ -1620,14 +1605,14 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>38231456</v>
+        <v>20730900</v>
       </c>
       <c r="D10" s="33" t="n"/>
       <c r="E10" s="33" t="n">
-        <v>-7.568</v>
+        <v>-3.367</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>0.296</v>
+        <v>0.132</v>
       </c>
     </row>
     <row r="11">
@@ -1642,14 +1627,14 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>13643614</v>
+        <v>11660079</v>
       </c>
       <c r="D11" s="33" t="n"/>
       <c r="E11" s="33" t="n">
-        <v>-1.181</v>
+        <v>-1.121</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>8.48</v>
+        <v>8.050000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -1664,14 +1649,14 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>26763360</v>
+        <v>28027772</v>
       </c>
       <c r="D12" s="33" t="n"/>
       <c r="E12" s="33" t="n">
-        <v>12.408</v>
+        <v>12.309</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>0.377</v>
+        <v>0.374</v>
       </c>
     </row>
     <row r="13">
@@ -1686,14 +1671,14 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>24985054</v>
+        <v>14204959</v>
       </c>
       <c r="D13" s="33" t="n"/>
       <c r="E13" s="33" t="n">
-        <v>-4.357</v>
+        <v>-3.483</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>0.358</v>
+        <v>0.287</v>
       </c>
     </row>
     <row r="15">
@@ -1741,9 +1726,7 @@
         </is>
       </c>
       <c r="D17" s="35" t="n"/>
-      <c r="E17" s="35" t="n">
-        <v>0</v>
-      </c>
+      <c r="E17" s="35" t="n"/>
       <c r="F17" s="35" t="n"/>
     </row>
     <row r="18">
